--- a/design/蛋仔--大富翁--机会表.xlsx
+++ b/design/蛋仔--大富翁--机会表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\eggitor\1_开发中\大富翁\设计文档\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\eggitor\1_开发中\大富翁\monopoly\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F48A938-FE24-4617-8733-471732D8B26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82395F4F-A91D-4A60-A7A3-1740B4503624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -240,10 +240,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>你去洗浴中心，支付1000金币。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>你投资失败，损失10000金币。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -313,6 +309,10 @@
   </si>
   <si>
     <t>若玩家已有座驾，检查已有座驾等级，若已有座驾等级大于更换的座驾，则不执行更换，否则顶掉原座驾。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你去游乐场，支付1000金币。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -398,8 +398,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -831,7 +831,7 @@
         <v>3005</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C7" s="3">
         <v>400</v>
@@ -854,7 +854,7 @@
         <v>3006</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="C8" s="3">
         <v>400</v>
@@ -923,7 +923,7 @@
         <v>3009</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11" s="3">
         <v>400</v>
@@ -946,7 +946,7 @@
         <v>3010</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C12" s="3">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>3012</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C14" s="3">
         <v>300</v>
@@ -1015,7 +1015,7 @@
         <v>3013</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C15" s="3">
         <v>300</v>
@@ -1061,7 +1061,7 @@
         <v>3015</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C17" s="3">
         <v>200</v>
@@ -1084,7 +1084,7 @@
         <v>3016</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C18" s="3">
         <v>200</v>
@@ -1291,7 +1291,7 @@
         <v>3025</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C27" s="3">
         <v>200</v>
@@ -1314,7 +1314,7 @@
         <v>3026</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C28" s="3">
         <v>200</v>
@@ -1337,7 +1337,7 @@
         <v>3027</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C29" s="3">
         <v>200</v>
@@ -1444,7 +1444,7 @@
         <v>44</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -1467,7 +1467,7 @@
         <v>44</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -1475,7 +1475,7 @@
         <v>3033</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C35" s="3">
         <v>200</v>
@@ -1490,7 +1490,7 @@
         <v>44</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -1498,7 +1498,7 @@
         <v>3034</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C36" s="3">
         <v>200</v>
@@ -1513,7 +1513,7 @@
         <v>44</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -1521,7 +1521,7 @@
         <v>3035</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C37" s="3">
         <v>100</v>
@@ -1539,7 +1539,7 @@
         <v>4004</v>
       </c>
       <c r="H37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
